--- a/analyses/Analisis_MSFT_GOOGL_PEP_v2.xlsx
+++ b/analyses/Analisis_MSFT_GOOGL_PEP_v2.xlsx
@@ -559,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I64"/>
+  <dimension ref="B1:I67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -932,308 +932,300 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; intangibles</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>77252</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>146817</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>142113</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>138986</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>For tangible book value (P/TBV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Operating cash flow</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n">
-        <v>169992</v>
-      </c>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Cash dividend paid</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>19800</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>21771</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>24082</v>
-      </c>
+          <t>Operating cash flow</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n">
-        <v>26249.33333333333</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Common dividends paid (outflow, shown positive)</t>
-        </is>
+        <v>169992</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Repurchase of capital stock</t>
+          <t>Cash dividend paid</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>22245</v>
+        <v>19800</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>17254</v>
+        <v>21771</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>18420</v>
+        <v>24082</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>23589.33333333333</v>
+        <v>26249.33333333333</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Buybacks (outflow, shown positive)</t>
+          <t>Common dividends paid (outflow, shown positive)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>CapEx</t>
+          <t>Repurchase of capital stock</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>28107</v>
+        <v>22245</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>44477</v>
+        <v>17254</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>64551</v>
+        <v>18420</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>112892</v>
+        <v>23589.33333333333</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Buybacks (outflow, shown positive)</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>28107</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>44477</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>64551</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>112892</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C27" s="9" t="n">
         <v>59475</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D27" s="9" t="n">
         <v>74071</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>71611</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>57100</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>MARKET DATA</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Total shares (diluted)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>7432</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>7434.13886</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>7434.15866</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>7434.15866</v>
-      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Market price</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>376.04</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>430.53</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>487.71</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>373.02</v>
+          <t>Total shares (diluted)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>7432</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>7434.13886</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>7434.15866</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>7434.15866</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Market price</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>430.53</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>487.71</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>373.02</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>Market cap.</t>
         </is>
       </c>
-      <c r="C30" s="9">
-        <f>C29*C28</f>
-        <v/>
-      </c>
-      <c r="D30" s="9">
-        <f>D29*D28</f>
-        <v/>
-      </c>
-      <c r="E30" s="9">
-        <f>E29*E28</f>
-        <v/>
-      </c>
-      <c r="F30" s="9">
-        <f>F29*F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="C31" s="9">
+        <f>C30*C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>D30*D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="9">
+        <f>E30*E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="9">
+        <f>F30*F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>VALUATION &amp; QUALITY RATIOS</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>1. Δ Revenue (YoY)</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11">
-        <f>D6/C6-1</f>
-        <v/>
-      </c>
-      <c r="E32" s="11">
-        <f>E6/D6-1</f>
-        <v/>
-      </c>
-      <c r="F32" s="11">
-        <f>F6/E6-1</f>
-        <v/>
-      </c>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="12">
-        <f>IF(NOT(ISNUMBER(F32)),"",IF(F32&gt;=0.1,"BUY",IF(F32&lt;0,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>YoY revenue growth</t>
-        </is>
-      </c>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2. Δ Net income (YoY)</t>
+          <t>1. Δ Revenue (YoY)</t>
         </is>
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11">
-        <f>IF(C9&lt;=0,"n.m.",D9/C9-1)</f>
+        <f>D6/C6-1</f>
         <v/>
       </c>
       <c r="E33" s="11">
-        <f>IF(D9&lt;=0,"n.m.",E9/D9-1)</f>
+        <f>E6/D6-1</f>
         <v/>
       </c>
       <c r="F33" s="11">
-        <f>IF(E9&lt;=0,"n.m.",F9/E9-1)</f>
-        <v/>
-      </c>
-      <c r="G33" s="11" t="n"/>
+        <f>F6/E6-1</f>
+        <v/>
+      </c>
       <c r="H33" s="12">
         <f>IF(NOT(ISNUMBER(F33)),"",IF(F33&gt;=0.1,"BUY",IF(F33&lt;0,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>YoY earnings growth (n.m. when prior year &lt;= 0)</t>
+          <t>YoY revenue growth</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>2. Δ Net income (YoY)</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11">
+        <f>IF(C9&lt;=0,1,D9/C9-1)</f>
+        <v/>
+      </c>
+      <c r="E34" s="11">
+        <f>IF(D9&lt;=0,1,E9/D9-1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="11">
+        <f>IF(E9&lt;=0,1,F9/E9-1)</f>
+        <v/>
+      </c>
+      <c r="H34" s="12">
+        <f>IF(NOT(ISNUMBER(F34)),"",IF(F34&gt;=0.1,"BUY",IF(F34&lt;0,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>YoY earnings growth (capped at +100% when prior year &lt;= 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>3. P/E (trailing)</t>
         </is>
       </c>
-      <c r="C34" s="13">
-        <f>C30/C9</f>
-        <v/>
-      </c>
-      <c r="D34" s="13">
-        <f>D30/D9</f>
-        <v/>
-      </c>
-      <c r="E34" s="13">
-        <f>E30/E9</f>
-        <v/>
-      </c>
-      <c r="F34" s="13">
-        <f>F30/F9</f>
-        <v/>
-      </c>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="12">
-        <f>IF(OR(G34="",NOT(ISNUMBER(F34)),F34&lt;=0),"",IF(F34&lt;G34*0.9,"BUY",IF(F34&gt;G34*1.1,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Market cap / net income; vs peer median</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Forward P/E</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n"/>
+      <c r="C35" s="13">
+        <f>C31/C9</f>
+        <v/>
+      </c>
       <c r="D35" s="13">
-        <f>IF(ISNUMBER(D33),D30/(D9*(1+D33)),D30/D9)</f>
+        <f>D31/D9</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(ISNUMBER(E33),E30/(E9*(1+E33)),E30/E9)</f>
+        <f>E31/E9</f>
         <v/>
       </c>
       <c r="F35" s="13">
-        <f>IF(ISNUMBER(F33),F30/(F9*(1+F33)),F30/F9)</f>
+        <f>F31/F9</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
@@ -1243,158 +1235,159 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>Market cap / net income; vs peer median</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Forward P/E</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13">
+        <f>IF(ISNUMBER(D34),D31/(D9*(1+D34)),D31/D9)</f>
+        <v/>
+      </c>
+      <c r="E36" s="13">
+        <f>IF(ISNUMBER(E34),E31/(E9*(1+E34)),E31/E9)</f>
+        <v/>
+      </c>
+      <c r="F36" s="13">
+        <f>IF(ISNUMBER(F34),F31/(F9*(1+F34)),F31/F9)</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="12">
+        <f>IF(OR(G36="",NOT(ISNUMBER(F36)),F36&lt;=0),"",IF(F36&lt;G36*0.9,"BUY",IF(F36&gt;G36*1.1,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>Market cap / (net income * (1 + earnings growth)); vs peer median</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>4. ROCE</t>
         </is>
       </c>
-      <c r="C36" s="11">
+      <c r="C37" s="11">
         <f>C8/C16</f>
         <v/>
       </c>
-      <c r="D36" s="11">
+      <c r="D37" s="11">
         <f>D8/D16</f>
         <v/>
       </c>
-      <c r="E36" s="11">
+      <c r="E37" s="11">
         <f>E8/E16</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="F37" s="11">
         <f>F8/F16</f>
         <v/>
       </c>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="12">
-        <f>IF(NOT(ISNUMBER(F36)),"",IF(F36&gt;=0.15,"BUY",IF(F36&lt;0.08,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="12">
+        <f>IF(NOT(ISNUMBER(F37)),"",IF(F37&gt;=0.15,"BUY",IF(F37&lt;0.08,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>EBIT / capital employed (&gt;=15% BUY, &lt;8% SELL)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Modified ROCE</t>
-        </is>
-      </c>
-      <c r="C37" s="11">
-        <f>C8/(C30-C17)</f>
-        <v/>
-      </c>
-      <c r="D37" s="11">
-        <f>D8/(D30-D17)</f>
-        <v/>
-      </c>
-      <c r="E37" s="11">
-        <f>E8/(E30-E17)</f>
-        <v/>
-      </c>
-      <c r="F37" s="11">
-        <f>F8/(F30-F17)</f>
-        <v/>
-      </c>
-      <c r="G37" s="11" t="n"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>EBIT / (market cap - equity)</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>5. EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C38" s="13">
-        <f>(C30+C18-C13)/C7</f>
-        <v/>
-      </c>
-      <c r="D38" s="13">
-        <f>(D30+D18-D13)/D7</f>
-        <v/>
-      </c>
-      <c r="E38" s="13">
-        <f>(E30+E18-E13)/E7</f>
-        <v/>
-      </c>
-      <c r="F38" s="13">
-        <f>(F30+F18-F13)/F7</f>
-        <v/>
-      </c>
-      <c r="G38" s="13" t="n"/>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ROE</t>
+        </is>
+      </c>
+      <c r="C38" s="11">
+        <f>C9/C17</f>
+        <v/>
+      </c>
+      <c r="D38" s="11">
+        <f>D9/D17</f>
+        <v/>
+      </c>
+      <c r="E38" s="11">
+        <f>E9/E17</f>
+        <v/>
+      </c>
+      <c r="F38" s="11">
+        <f>F9/F17</f>
+        <v/>
+      </c>
+      <c r="G38" s="11" t="n"/>
       <c r="H38" s="12">
-        <f>IF(OR(G38="",NOT(ISNUMBER(F38)),F38&lt;=0),"",IF(F38&lt;G38*0.9,"BUY",IF(F38&gt;G38*1.1,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F38)),"",IF(F38&gt;=0.15,"BUY",IF(F38&lt;0.08,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value / EBITDA; vs peer median</t>
+          <t>Net income / equity — works for banks (&gt;=15% BUY, &lt;8% SELL)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>6. P / B</t>
-        </is>
-      </c>
-      <c r="C39" s="13">
-        <f>C30/C17</f>
-        <v/>
-      </c>
-      <c r="D39" s="13">
-        <f>D30/D17</f>
-        <v/>
-      </c>
-      <c r="E39" s="13">
-        <f>E30/E17</f>
-        <v/>
-      </c>
-      <c r="F39" s="13">
-        <f>F30/F17</f>
-        <v/>
-      </c>
-      <c r="G39" s="13" t="n"/>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Acid ROCE</t>
+        </is>
+      </c>
+      <c r="C39" s="11">
+        <f>C8/(C31-C17)</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>D8/(D31-D17)</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>E8/(E31-E17)</f>
+        <v/>
+      </c>
+      <c r="F39" s="11">
+        <f>F8/(F31-F17)</f>
+        <v/>
+      </c>
+      <c r="G39" s="11" t="n"/>
       <c r="H39" s="12">
-        <f>IF(OR(G39="",NOT(ISNUMBER(F39)),F39&lt;=0),"",IF(F39&lt;G39*0.9,"BUY",IF(F39&gt;G39*1.1,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F39)),"",IF(F39&gt;=0.05,"BUY",IF(F39&lt;0.04,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>vs peer median</t>
+          <t>EBIT / (market cap - equity) (&gt;=5% BUY, 4-5% HOLD, &lt;4% SELL)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>7. P / S</t>
+          <t>5. EV / EBITDA</t>
         </is>
       </c>
       <c r="C40" s="13">
-        <f>C30/C6</f>
+        <f>(C31+C18-C13)/C7</f>
         <v/>
       </c>
       <c r="D40" s="13">
-        <f>D30/D6</f>
+        <f>(D31+D18-D13)/D7</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>E30/E6</f>
+        <f>(E31+E18-E13)/E7</f>
         <v/>
       </c>
       <c r="F40" s="13">
-        <f>F30/F6</f>
+        <f>(F31+F18-F13)/F7</f>
         <v/>
       </c>
       <c r="G40" s="13" t="n"/>
@@ -1404,30 +1397,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>vs peer median</t>
+          <t>Enterprise value / EBITDA; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>8. EV / FCF</t>
+          <t>6. P / B</t>
         </is>
       </c>
       <c r="C41" s="13">
-        <f>(C30+C18-C13)/C26</f>
+        <f>C31/C17</f>
         <v/>
       </c>
       <c r="D41" s="13">
-        <f>(D30+D18-D13)/D26</f>
+        <f>D31/D17</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>(E30+E18-E13)/E26</f>
+        <f>E31/E17</f>
         <v/>
       </c>
       <c r="F41" s="13">
-        <f>(F30+F18-F13)/F26</f>
+        <f>F31/F17</f>
         <v/>
       </c>
       <c r="G41" s="13" t="n"/>
@@ -1442,334 +1435,439 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>9. Dividend yield</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>0.0166</v>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="F42" s="15" t="n"/>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P / TBV</t>
+        </is>
+      </c>
+      <c r="C42" s="13">
+        <f>C31/(C17-C21)</f>
+        <v/>
+      </c>
+      <c r="D42" s="13">
+        <f>D31/(D17-D21)</f>
+        <v/>
+      </c>
+      <c r="E42" s="13">
+        <f>E31/(E17-E21)</f>
+        <v/>
+      </c>
+      <c r="F42" s="13">
+        <f>F31/(F17-F21)</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="12">
-        <f>IF(NOT(ISNUMBER(F42)),"",IF(F42&gt;=0.03,"BUY",IF(F42&lt;0.01,"SELL","HOLD")))</f>
+        <f>IF(OR(G42="",NOT(ISNUMBER(F42)),F42&lt;=0),"",IF(F42&lt;G42*0.9,"BUY",IF(F42&gt;G42*1.1,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>&gt;=3% BUY, &lt;1% SELL</t>
+          <t>Price / tangible book — key for banks; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>10. Total shareholder return</t>
-        </is>
-      </c>
-      <c r="C43" s="11">
-        <f>(C23+C24)/C30</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
-        <f>(D23+D24)/D30</f>
-        <v/>
-      </c>
-      <c r="E43" s="11">
-        <f>(E23+E24)/E30</f>
-        <v/>
-      </c>
-      <c r="F43" s="11">
-        <f>(F23+F24)/F30</f>
-        <v/>
-      </c>
-      <c r="G43" s="11" t="n"/>
+          <t>7. P / S</t>
+        </is>
+      </c>
+      <c r="C43" s="13">
+        <f>C31/C6</f>
+        <v/>
+      </c>
+      <c r="D43" s="13">
+        <f>D31/D6</f>
+        <v/>
+      </c>
+      <c r="E43" s="13">
+        <f>E31/E6</f>
+        <v/>
+      </c>
+      <c r="F43" s="13">
+        <f>F31/F6</f>
+        <v/>
+      </c>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="12">
-        <f>IF(NOT(ISNUMBER(F43)),"",IF(F43&gt;=0.05,"BUY",IF(F43&lt;0.02,"SELL","HOLD")))</f>
+        <f>IF(OR(G43="",NOT(ISNUMBER(F43)),F43&lt;=0),"",IF(F43&lt;G43*0.9,"BUY",IF(F43&gt;G43*1.1,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>(dividends + buybacks) / market cap (&gt;=5% BUY, &lt;2% SELL)</t>
+          <t>vs peer median</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>11. CapEx / EBITDA</t>
-        </is>
-      </c>
-      <c r="C44" s="11">
-        <f>C25/C7</f>
-        <v/>
-      </c>
-      <c r="D44" s="11">
-        <f>D25/D7</f>
-        <v/>
-      </c>
-      <c r="E44" s="11">
-        <f>E25/E7</f>
-        <v/>
-      </c>
-      <c r="F44" s="11">
-        <f>F25/F7</f>
-        <v/>
-      </c>
-      <c r="G44" s="11" t="n"/>
+          <t>8. EV / FCF</t>
+        </is>
+      </c>
+      <c r="C44" s="13">
+        <f>(C31+C18-C13)/C27</f>
+        <v/>
+      </c>
+      <c r="D44" s="13">
+        <f>(D31+D18-D13)/D27</f>
+        <v/>
+      </c>
+      <c r="E44" s="13">
+        <f>(E31+E18-E13)/E27</f>
+        <v/>
+      </c>
+      <c r="F44" s="13">
+        <f>(F31+F18-F13)/F27</f>
+        <v/>
+      </c>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="12">
+        <f>IF(OR(G44="",NOT(ISNUMBER(F44)),F44&lt;=0),"",IF(F44&lt;G44*0.9,"BUY",IF(F44&gt;G44*1.1,"SELL","HOLD")))</f>
+        <v/>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>informational; vs peer median</t>
+          <t>vs peer median</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>12. CapEx / D&amp;A</t>
-        </is>
-      </c>
-      <c r="C45" s="13">
-        <f>C25/C10</f>
-        <v/>
-      </c>
-      <c r="D45" s="13">
-        <f>D25/D10</f>
-        <v/>
-      </c>
-      <c r="E45" s="13">
-        <f>E25/E10</f>
-        <v/>
-      </c>
-      <c r="F45" s="13">
-        <f>F25/F10</f>
-        <v/>
-      </c>
-      <c r="G45" s="13" t="n"/>
+          <t>9. Dividend yield</t>
+        </is>
+      </c>
+      <c r="C45" s="15">
+        <f>C24/C31</f>
+        <v/>
+      </c>
+      <c r="D45" s="15">
+        <f>D24/D31</f>
+        <v/>
+      </c>
+      <c r="E45" s="15">
+        <f>E24/E31</f>
+        <v/>
+      </c>
+      <c r="F45" s="15">
+        <f>F24/F31</f>
+        <v/>
+      </c>
+      <c r="H45" s="12">
+        <f>IF(NOT(ISNUMBER(F45)),"",IF(F45&gt;=0.03,"BUY",IF(F45&lt;0.01,"SELL","HOLD")))</f>
+        <v/>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>informational; vs peer median</t>
+          <t>Dividends paid / market cap (&gt;=3% BUY, &lt;1% SELL)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>13. Ratio de endeudamiento</t>
+          <t>10. Total shareholder return</t>
         </is>
       </c>
       <c r="C46" s="11">
-        <f>C19/C12</f>
+        <f>(C24+C25)/C31</f>
         <v/>
       </c>
       <c r="D46" s="11">
-        <f>D19/D12</f>
+        <f>(D24+D25)/D31</f>
         <v/>
       </c>
       <c r="E46" s="11">
-        <f>E19/E12</f>
+        <f>(E24+E25)/E31</f>
         <v/>
       </c>
       <c r="F46" s="11">
-        <f>F19/F12</f>
+        <f>(F24+F25)/F31</f>
         <v/>
       </c>
       <c r="G46" s="11" t="n"/>
       <c r="H46" s="12">
-        <f>IF(NOT(ISNUMBER(F46)),"",IF(F46&lt;=0.3,"BUY",IF(F46&gt;0.6,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F46)),"",IF(F46&gt;=0.05,"BUY",IF(F46&lt;0.02,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Total debt / total assets (&lt;=30% BUY, &gt;60% SELL)</t>
+          <t>(dividends + buybacks) / market cap (&gt;=5% BUY, &lt;2% SELL)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>14. Deuda financiera neta / activos (libros)</t>
+          <t>11. CapEx / EBITDA</t>
         </is>
       </c>
       <c r="C47" s="11">
-        <f>C20/(C20+C12)</f>
+        <f>C26/C7</f>
         <v/>
       </c>
       <c r="D47" s="11">
-        <f>D20/(D20+D12)</f>
+        <f>D26/D7</f>
         <v/>
       </c>
       <c r="E47" s="11">
-        <f>E20/(E20+E12)</f>
+        <f>E26/E7</f>
         <v/>
       </c>
       <c r="F47" s="11">
-        <f>F20/(F20+F12)</f>
+        <f>F26/F7</f>
         <v/>
       </c>
       <c r="G47" s="11" t="n"/>
-      <c r="H47" s="12">
-        <f>IF(NOT(ISNUMBER(F47)),"",IF(F47&lt;=0.2,"BUY",IF(F47&gt;0.4,"SELL","HOLD")))</f>
-        <v/>
-      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Net debt / (net debt + total assets) (&lt;=20% BUY, &gt;40% SELL)</t>
+          <t>informational; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>15. Deuda financiera neta / market cap</t>
-        </is>
-      </c>
-      <c r="C48" s="11">
-        <f>C20/C30</f>
-        <v/>
-      </c>
-      <c r="D48" s="11">
-        <f>D20/D30</f>
-        <v/>
-      </c>
-      <c r="E48" s="11">
-        <f>E20/E30</f>
-        <v/>
-      </c>
-      <c r="F48" s="11">
-        <f>F20/F30</f>
-        <v/>
-      </c>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="12">
-        <f>IF(NOT(ISNUMBER(F48)),"",IF(F48&lt;=0.15,"BUY",IF(F48&gt;0.4,"SELL","HOLD")))</f>
-        <v/>
-      </c>
+          <t>12. CapEx / D&amp;A</t>
+        </is>
+      </c>
+      <c r="C48" s="13">
+        <f>C26/C10</f>
+        <v/>
+      </c>
+      <c r="D48" s="13">
+        <f>D26/D10</f>
+        <v/>
+      </c>
+      <c r="E48" s="13">
+        <f>E26/E10</f>
+        <v/>
+      </c>
+      <c r="F48" s="13">
+        <f>F26/F10</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="n"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Net debt / market cap (&lt;=15% BUY, &gt;40% SELL)</t>
+          <t>informational; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="8" t="inlineStr">
         <is>
+          <t>13. Ratio de endeudamiento</t>
+        </is>
+      </c>
+      <c r="C49" s="11">
+        <f>C19/C12</f>
+        <v/>
+      </c>
+      <c r="D49" s="11">
+        <f>D19/D12</f>
+        <v/>
+      </c>
+      <c r="E49" s="11">
+        <f>E19/E12</f>
+        <v/>
+      </c>
+      <c r="F49" s="11">
+        <f>F19/F12</f>
+        <v/>
+      </c>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="12">
+        <f>IF(NOT(ISNUMBER(F49)),"",IF(F49&lt;=0.3,"BUY",IF(F49&gt;0.6,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Total debt / total assets (&lt;=30% BUY, &gt;60% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>14. Deuda financiera neta / activos (libros)</t>
+        </is>
+      </c>
+      <c r="C50" s="11">
+        <f>C20/(C20+C12)</f>
+        <v/>
+      </c>
+      <c r="D50" s="11">
+        <f>D20/(D20+D12)</f>
+        <v/>
+      </c>
+      <c r="E50" s="11">
+        <f>E20/(E20+E12)</f>
+        <v/>
+      </c>
+      <c r="F50" s="11">
+        <f>F20/(F20+F12)</f>
+        <v/>
+      </c>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="12">
+        <f>IF(NOT(ISNUMBER(F50)),"",IF(F50&lt;=0.2,"BUY",IF(F50&gt;0.4,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / (net debt + total assets) (&lt;=20% BUY, &gt;40% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>15. Deuda financiera neta / market cap</t>
+        </is>
+      </c>
+      <c r="C51" s="11">
+        <f>C20/C31</f>
+        <v/>
+      </c>
+      <c r="D51" s="11">
+        <f>D20/D31</f>
+        <v/>
+      </c>
+      <c r="E51" s="11">
+        <f>E20/E31</f>
+        <v/>
+      </c>
+      <c r="F51" s="11">
+        <f>F20/F31</f>
+        <v/>
+      </c>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="12">
+        <f>IF(NOT(ISNUMBER(F51)),"",IF(F51&lt;=0.15,"BUY",IF(F51&gt;0.4,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / market cap (&lt;=15% BUY, &gt;40% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
+        <is>
           <t>16. Price estimate (Trefis)</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="H49" s="12">
-        <f>IF(OR(F49="",F29=""),"",IF(F49&gt;F29*1.1,"BUY",IF(F49&lt;F29*0.9,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="H52" s="12">
+        <f>IF(OR(F52="",F30=""),"",IF(F52&gt;F30*1.1,"BUY",IF(F52&lt;F30*0.9,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>External target vs price (&gt;+10% BUY, &lt;-10% SELL)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="16" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Run-rate: 2026-03 (run-rate) annualizes reported year-to-date flows; balance-sheet items are the latest reported quarter (point-in-time).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="17" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Reorganized from Analisis_MSFT_GOOGL_PEP.xlsx (MSFT converted from thousands to millions). Total debt / net debt / dividends / buybacks back-filled from Yahoo Finance.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="B54" s="18" t="inlineStr">
+    <row r="57">
+      <c r="B57" s="18" t="inlineStr">
         <is>
           <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="19" t="inlineStr">
-        <is>
-          <t>• Gross y Operating Margins cayendo 1 a 2 pp, pero estables en el rango 67-69 y 47-49</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="19" t="inlineStr">
-        <is>
-          <t>• Guidance Q4 25: aumento sustancial del CapEx (&gt;$30 bn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="19" t="inlineStr">
-        <is>
-          <t>• Guidance Q1 26: CapEx a superar 2025 por fuerte demanda</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="19" t="inlineStr">
         <is>
-          <t>• MSFT tiene un 27% de participación en OpenAI</t>
+          <t>• Gross y Operating Margins cayendo 1 a 2 pp, pero estables en el rango 67-69 y 47-49</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="19" t="inlineStr">
         <is>
-          <t>• OpenAI hizo pedio a SEC para salir en bolsa de manera confidencial.</t>
+          <t>• Guidance Q4 25: aumento sustancial del CapEx (&gt;$30 bn)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="19" t="inlineStr">
         <is>
-          <t>• Los balances filtrados parecen mostrar pérdidas por $24bn en 2025 (ingresos por 10 y gastos por 34)</t>
+          <t>• Guidance Q1 26: CapEx a superar 2025 por fuerte demanda</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="19" t="inlineStr">
         <is>
-          <t>• No le dan los ingresos para justificar la valuación a la que apunta: tendría que ganar todo el market-share de ads ($101 bn) para 2030</t>
+          <t>• MSFT tiene un 27% de participación en OpenAI</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="19" t="inlineStr">
         <is>
-          <t>• Planea aumentar el revenue por ads desde $2bn hoy a $102 bn en 2030</t>
+          <t>• OpenAI hizo pedio a SEC para salir en bolsa de manera confidencial.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="19" t="inlineStr">
         <is>
-          <t>• 72% del costo del revenue viene de MSFT: mercado lee conflicto de interés</t>
+          <t>• Los balances filtrados parecen mostrar pérdidas por $24bn en 2025 (ingresos por 10 y gastos por 34)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="19" t="inlineStr">
         <is>
+          <t>• No le dan los ingresos para justificar la valuación a la que apunta: tendría que ganar todo el market-share de ads ($101 bn) para 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" s="19" t="inlineStr">
+        <is>
+          <t>• Planea aumentar el revenue por ads desde $2bn hoy a $102 bn en 2030</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="19" t="inlineStr">
+        <is>
+          <t>• 72% del costo del revenue viene de MSFT: mercado lee conflicto de interés</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="19" t="inlineStr">
+        <is>
           <t>• Market share de API volume cayó fuerte de 70-85% a 45-60%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H5:H50">
+  <conditionalFormatting sqref="H5:H53">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BUY"</formula>
     </cfRule>
@@ -1790,7 +1888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I52"/>
+  <dimension ref="B1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -2163,308 +2261,300 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; intangibles</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>32657</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>32335</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>33982</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>34164</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>For tangible book value (P/TBV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Operating cash flow</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n">
-        <v>13101</v>
-      </c>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Cash dividend paid</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>6682</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>7229</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>7638</v>
-      </c>
+          <t>Operating cash flow</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n">
-        <v>7864</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Common dividends paid (outflow, shown positive)</t>
-        </is>
+        <v>13101</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Repurchase of capital stock</t>
+          <t>Cash dividend paid</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1000</v>
+        <v>6682</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1000</v>
+        <v>7229</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>1000</v>
+        <v>7638</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>728</v>
+        <v>7864</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Buybacks (outflow, shown positive)</t>
+          <t>Common dividends paid (outflow, shown positive)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>CapEx</t>
+          <t>Repurchase of capital stock</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>5518</v>
+        <v>1000</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>5318</v>
+        <v>1000</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>4415</v>
+        <v>1000</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>4259</v>
+        <v>728</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Buybacks (outflow, shown positive)</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>5518</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>5318</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>4415</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C27" s="9" t="n">
         <v>7924</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D27" s="9" t="n">
         <v>7189</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>7672</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>8842</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>MARKET DATA</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Total shares (diluted)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>1376</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>1373</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>1369</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>1370</v>
-      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Market price</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>169.84</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>152.03</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>135.4</v>
+          <t>Total shares (diluted)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1376</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1373</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>1369</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Market price</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>169.84</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>152.03</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>135.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>Market cap.</t>
         </is>
       </c>
-      <c r="C30" s="9">
-        <f>C29*C28</f>
-        <v/>
-      </c>
-      <c r="D30" s="9">
-        <f>D29*D28</f>
-        <v/>
-      </c>
-      <c r="E30" s="9">
-        <f>E29*E28</f>
-        <v/>
-      </c>
-      <c r="F30" s="9">
-        <f>F29*F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="C31" s="9">
+        <f>C30*C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>D30*D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="9">
+        <f>E30*E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="9">
+        <f>F30*F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>VALUATION &amp; QUALITY RATIOS</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>1. Δ Revenue (YoY)</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11">
-        <f>D6/C6-1</f>
-        <v/>
-      </c>
-      <c r="E32" s="11">
-        <f>E6/D6-1</f>
-        <v/>
-      </c>
-      <c r="F32" s="11">
-        <f>F6/E6-1</f>
-        <v/>
-      </c>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="12">
-        <f>IF(NOT(ISNUMBER(F32)),"",IF(F32&gt;=0.1,"BUY",IF(F32&lt;0,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>YoY revenue growth</t>
-        </is>
-      </c>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2. Δ Net income (YoY)</t>
+          <t>1. Δ Revenue (YoY)</t>
         </is>
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11">
-        <f>IF(C9&lt;=0,"n.m.",D9/C9-1)</f>
+        <f>D6/C6-1</f>
         <v/>
       </c>
       <c r="E33" s="11">
-        <f>IF(D9&lt;=0,"n.m.",E9/D9-1)</f>
+        <f>E6/D6-1</f>
         <v/>
       </c>
       <c r="F33" s="11">
-        <f>IF(E9&lt;=0,"n.m.",F9/E9-1)</f>
-        <v/>
-      </c>
-      <c r="G33" s="11" t="n"/>
+        <f>F6/E6-1</f>
+        <v/>
+      </c>
       <c r="H33" s="12">
         <f>IF(NOT(ISNUMBER(F33)),"",IF(F33&gt;=0.1,"BUY",IF(F33&lt;0,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>YoY earnings growth (n.m. when prior year &lt;= 0)</t>
+          <t>YoY revenue growth</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>2. Δ Net income (YoY)</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11">
+        <f>IF(C9&lt;=0,1,D9/C9-1)</f>
+        <v/>
+      </c>
+      <c r="E34" s="11">
+        <f>IF(D9&lt;=0,1,E9/D9-1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="11">
+        <f>IF(E9&lt;=0,1,F9/E9-1)</f>
+        <v/>
+      </c>
+      <c r="H34" s="12">
+        <f>IF(NOT(ISNUMBER(F34)),"",IF(F34&gt;=0.1,"BUY",IF(F34&lt;0,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>YoY earnings growth (capped at +100% when prior year &lt;= 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>3. P/E (trailing)</t>
         </is>
       </c>
-      <c r="C34" s="13">
-        <f>C30/C9</f>
-        <v/>
-      </c>
-      <c r="D34" s="13">
-        <f>D30/D9</f>
-        <v/>
-      </c>
-      <c r="E34" s="13">
-        <f>E30/E9</f>
-        <v/>
-      </c>
-      <c r="F34" s="13">
-        <f>F30/F9</f>
-        <v/>
-      </c>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="12">
-        <f>IF(OR(G34="",NOT(ISNUMBER(F34)),F34&lt;=0),"",IF(F34&lt;G34*0.9,"BUY",IF(F34&gt;G34*1.1,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Market cap / net income; vs peer median</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Forward P/E</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n"/>
+      <c r="C35" s="13">
+        <f>C31/C9</f>
+        <v/>
+      </c>
       <c r="D35" s="13">
-        <f>IF(ISNUMBER(D33),D30/(D9*(1+D33)),D30/D9)</f>
+        <f>D31/D9</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(ISNUMBER(E33),E30/(E9*(1+E33)),E30/E9)</f>
+        <f>E31/E9</f>
         <v/>
       </c>
       <c r="F35" s="13">
-        <f>IF(ISNUMBER(F33),F30/(F9*(1+F33)),F30/F9)</f>
+        <f>F31/F9</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
@@ -2474,158 +2564,159 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>Market cap / net income; vs peer median</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Forward P/E</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13">
+        <f>IF(ISNUMBER(D34),D31/(D9*(1+D34)),D31/D9)</f>
+        <v/>
+      </c>
+      <c r="E36" s="13">
+        <f>IF(ISNUMBER(E34),E31/(E9*(1+E34)),E31/E9)</f>
+        <v/>
+      </c>
+      <c r="F36" s="13">
+        <f>IF(ISNUMBER(F34),F31/(F9*(1+F34)),F31/F9)</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="12">
+        <f>IF(OR(G36="",NOT(ISNUMBER(F36)),F36&lt;=0),"",IF(F36&lt;G36*0.9,"BUY",IF(F36&gt;G36*1.1,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>Market cap / (net income * (1 + earnings growth)); vs peer median</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>4. ROCE</t>
         </is>
       </c>
-      <c r="C36" s="11">
+      <c r="C37" s="11">
         <f>C8/C16</f>
         <v/>
       </c>
-      <c r="D36" s="11">
+      <c r="D37" s="11">
         <f>D8/D16</f>
         <v/>
       </c>
-      <c r="E36" s="11">
+      <c r="E37" s="11">
         <f>E8/E16</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="F37" s="11">
         <f>F8/F16</f>
         <v/>
       </c>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="12">
-        <f>IF(NOT(ISNUMBER(F36)),"",IF(F36&gt;=0.15,"BUY",IF(F36&lt;0.08,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="12">
+        <f>IF(NOT(ISNUMBER(F37)),"",IF(F37&gt;=0.15,"BUY",IF(F37&lt;0.08,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>EBIT / capital employed (&gt;=15% BUY, &lt;8% SELL)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Modified ROCE</t>
-        </is>
-      </c>
-      <c r="C37" s="11">
-        <f>C8/(C30-C17)</f>
-        <v/>
-      </c>
-      <c r="D37" s="11">
-        <f>D8/(D30-D17)</f>
-        <v/>
-      </c>
-      <c r="E37" s="11">
-        <f>E8/(E30-E17)</f>
-        <v/>
-      </c>
-      <c r="F37" s="11">
-        <f>F8/(F30-F17)</f>
-        <v/>
-      </c>
-      <c r="G37" s="11" t="n"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>EBIT / (market cap - equity)</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>5. EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C38" s="13">
-        <f>(C30+C18-C13)/C7</f>
-        <v/>
-      </c>
-      <c r="D38" s="13">
-        <f>(D30+D18-D13)/D7</f>
-        <v/>
-      </c>
-      <c r="E38" s="13">
-        <f>(E30+E18-E13)/E7</f>
-        <v/>
-      </c>
-      <c r="F38" s="13">
-        <f>(F30+F18-F13)/F7</f>
-        <v/>
-      </c>
-      <c r="G38" s="13" t="n"/>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ROE</t>
+        </is>
+      </c>
+      <c r="C38" s="11">
+        <f>C9/C17</f>
+        <v/>
+      </c>
+      <c r="D38" s="11">
+        <f>D9/D17</f>
+        <v/>
+      </c>
+      <c r="E38" s="11">
+        <f>E9/E17</f>
+        <v/>
+      </c>
+      <c r="F38" s="11">
+        <f>F9/F17</f>
+        <v/>
+      </c>
+      <c r="G38" s="11" t="n"/>
       <c r="H38" s="12">
-        <f>IF(OR(G38="",NOT(ISNUMBER(F38)),F38&lt;=0),"",IF(F38&lt;G38*0.9,"BUY",IF(F38&gt;G38*1.1,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F38)),"",IF(F38&gt;=0.15,"BUY",IF(F38&lt;0.08,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value / EBITDA; vs peer median</t>
+          <t>Net income / equity — works for banks (&gt;=15% BUY, &lt;8% SELL)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>6. P / B</t>
-        </is>
-      </c>
-      <c r="C39" s="13">
-        <f>C30/C17</f>
-        <v/>
-      </c>
-      <c r="D39" s="13">
-        <f>D30/D17</f>
-        <v/>
-      </c>
-      <c r="E39" s="13">
-        <f>E30/E17</f>
-        <v/>
-      </c>
-      <c r="F39" s="13">
-        <f>F30/F17</f>
-        <v/>
-      </c>
-      <c r="G39" s="13" t="n"/>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Acid ROCE</t>
+        </is>
+      </c>
+      <c r="C39" s="11">
+        <f>C8/(C31-C17)</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>D8/(D31-D17)</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>E8/(E31-E17)</f>
+        <v/>
+      </c>
+      <c r="F39" s="11">
+        <f>F8/(F31-F17)</f>
+        <v/>
+      </c>
+      <c r="G39" s="11" t="n"/>
       <c r="H39" s="12">
-        <f>IF(OR(G39="",NOT(ISNUMBER(F39)),F39&lt;=0),"",IF(F39&lt;G39*0.9,"BUY",IF(F39&gt;G39*1.1,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F39)),"",IF(F39&gt;=0.05,"BUY",IF(F39&lt;0.04,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>vs peer median</t>
+          <t>EBIT / (market cap - equity) (&gt;=5% BUY, 4-5% HOLD, &lt;4% SELL)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>7. P / S</t>
+          <t>5. EV / EBITDA</t>
         </is>
       </c>
       <c r="C40" s="13">
-        <f>C30/C6</f>
+        <f>(C31+C18-C13)/C7</f>
         <v/>
       </c>
       <c r="D40" s="13">
-        <f>D30/D6</f>
+        <f>(D31+D18-D13)/D7</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>E30/E6</f>
+        <f>(E31+E18-E13)/E7</f>
         <v/>
       </c>
       <c r="F40" s="13">
-        <f>F30/F6</f>
+        <f>(F31+F18-F13)/F7</f>
         <v/>
       </c>
       <c r="G40" s="13" t="n"/>
@@ -2635,30 +2726,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>vs peer median</t>
+          <t>Enterprise value / EBITDA; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>8. EV / FCF</t>
+          <t>6. P / B</t>
         </is>
       </c>
       <c r="C41" s="13">
-        <f>(C30+C18-C13)/C26</f>
+        <f>C31/C17</f>
         <v/>
       </c>
       <c r="D41" s="13">
-        <f>(D30+D18-D13)/D26</f>
+        <f>D31/D17</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>(E30+E18-E13)/E26</f>
+        <f>E31/E17</f>
         <v/>
       </c>
       <c r="F41" s="13">
-        <f>(F30+F18-F13)/F26</f>
+        <f>F31/F17</f>
         <v/>
       </c>
       <c r="G41" s="13" t="n"/>
@@ -2673,257 +2764,362 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>9. Dividend yield</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>0.0291156382477626</v>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>0.0350588699598763</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.0391504178272981</v>
-      </c>
-      <c r="F42" s="15" t="n"/>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P / TBV</t>
+        </is>
+      </c>
+      <c r="C42" s="13">
+        <f>C31/(C17-C21)</f>
+        <v/>
+      </c>
+      <c r="D42" s="13">
+        <f>D31/(D17-D21)</f>
+        <v/>
+      </c>
+      <c r="E42" s="13">
+        <f>E31/(E17-E21)</f>
+        <v/>
+      </c>
+      <c r="F42" s="13">
+        <f>F31/(F17-F21)</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="12">
-        <f>IF(NOT(ISNUMBER(F42)),"",IF(F42&gt;=0.03,"BUY",IF(F42&lt;0.01,"SELL","HOLD")))</f>
+        <f>IF(OR(G42="",NOT(ISNUMBER(F42)),F42&lt;=0),"",IF(F42&lt;G42*0.9,"BUY",IF(F42&gt;G42*1.1,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>&gt;=3% BUY, &lt;1% SELL</t>
+          <t>Price / tangible book — key for banks; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>10. Total shareholder return</t>
-        </is>
-      </c>
-      <c r="C43" s="11">
-        <f>(C23+C24)/C30</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
-        <f>(D23+D24)/D30</f>
-        <v/>
-      </c>
-      <c r="E43" s="11">
-        <f>(E23+E24)/E30</f>
-        <v/>
-      </c>
-      <c r="F43" s="11">
-        <f>(F23+F24)/F30</f>
-        <v/>
-      </c>
-      <c r="G43" s="11" t="n"/>
+          <t>7. P / S</t>
+        </is>
+      </c>
+      <c r="C43" s="13">
+        <f>C31/C6</f>
+        <v/>
+      </c>
+      <c r="D43" s="13">
+        <f>D31/D6</f>
+        <v/>
+      </c>
+      <c r="E43" s="13">
+        <f>E31/E6</f>
+        <v/>
+      </c>
+      <c r="F43" s="13">
+        <f>F31/F6</f>
+        <v/>
+      </c>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="12">
-        <f>IF(NOT(ISNUMBER(F43)),"",IF(F43&gt;=0.05,"BUY",IF(F43&lt;0.02,"SELL","HOLD")))</f>
+        <f>IF(OR(G43="",NOT(ISNUMBER(F43)),F43&lt;=0),"",IF(F43&lt;G43*0.9,"BUY",IF(F43&gt;G43*1.1,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>(dividends + buybacks) / market cap (&gt;=5% BUY, &lt;2% SELL)</t>
+          <t>vs peer median</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>11. CapEx / EBITDA</t>
-        </is>
-      </c>
-      <c r="C44" s="11">
-        <f>C25/C7</f>
-        <v/>
-      </c>
-      <c r="D44" s="11">
-        <f>D25/D7</f>
-        <v/>
-      </c>
-      <c r="E44" s="11">
-        <f>E25/E7</f>
-        <v/>
-      </c>
-      <c r="F44" s="11">
-        <f>F25/F7</f>
-        <v/>
-      </c>
-      <c r="G44" s="11" t="n"/>
+          <t>8. EV / FCF</t>
+        </is>
+      </c>
+      <c r="C44" s="13">
+        <f>(C31+C18-C13)/C27</f>
+        <v/>
+      </c>
+      <c r="D44" s="13">
+        <f>(D31+D18-D13)/D27</f>
+        <v/>
+      </c>
+      <c r="E44" s="13">
+        <f>(E31+E18-E13)/E27</f>
+        <v/>
+      </c>
+      <c r="F44" s="13">
+        <f>(F31+F18-F13)/F27</f>
+        <v/>
+      </c>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="12">
+        <f>IF(OR(G44="",NOT(ISNUMBER(F44)),F44&lt;=0),"",IF(F44&lt;G44*0.9,"BUY",IF(F44&gt;G44*1.1,"SELL","HOLD")))</f>
+        <v/>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>informational; vs peer median</t>
+          <t>vs peer median</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>12. CapEx / D&amp;A</t>
-        </is>
-      </c>
-      <c r="C45" s="13">
-        <f>C25/C10</f>
-        <v/>
-      </c>
-      <c r="D45" s="13">
-        <f>D25/D10</f>
-        <v/>
-      </c>
-      <c r="E45" s="13">
-        <f>E25/E10</f>
-        <v/>
-      </c>
-      <c r="F45" s="13">
-        <f>F25/F10</f>
-        <v/>
-      </c>
-      <c r="G45" s="13" t="n"/>
+          <t>9. Dividend yield</t>
+        </is>
+      </c>
+      <c r="C45" s="15">
+        <f>C24/C31</f>
+        <v/>
+      </c>
+      <c r="D45" s="15">
+        <f>D24/D31</f>
+        <v/>
+      </c>
+      <c r="E45" s="15">
+        <f>E24/E31</f>
+        <v/>
+      </c>
+      <c r="F45" s="15">
+        <f>F24/F31</f>
+        <v/>
+      </c>
+      <c r="H45" s="12">
+        <f>IF(NOT(ISNUMBER(F45)),"",IF(F45&gt;=0.03,"BUY",IF(F45&lt;0.01,"SELL","HOLD")))</f>
+        <v/>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>informational; vs peer median</t>
+          <t>Dividends paid / market cap (&gt;=3% BUY, &lt;1% SELL)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>13. Ratio de endeudamiento</t>
+          <t>10. Total shareholder return</t>
         </is>
       </c>
       <c r="C46" s="11">
-        <f>C19/C12</f>
+        <f>(C24+C25)/C31</f>
         <v/>
       </c>
       <c r="D46" s="11">
-        <f>D19/D12</f>
+        <f>(D24+D25)/D31</f>
         <v/>
       </c>
       <c r="E46" s="11">
-        <f>E19/E12</f>
+        <f>(E24+E25)/E31</f>
         <v/>
       </c>
       <c r="F46" s="11">
-        <f>F19/F12</f>
+        <f>(F24+F25)/F31</f>
         <v/>
       </c>
       <c r="G46" s="11" t="n"/>
       <c r="H46" s="12">
-        <f>IF(NOT(ISNUMBER(F46)),"",IF(F46&lt;=0.3,"BUY",IF(F46&gt;0.6,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F46)),"",IF(F46&gt;=0.05,"BUY",IF(F46&lt;0.02,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Total debt / total assets (&lt;=30% BUY, &gt;60% SELL)</t>
+          <t>(dividends + buybacks) / market cap (&gt;=5% BUY, &lt;2% SELL)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>14. Deuda financiera neta / activos (libros)</t>
+          <t>11. CapEx / EBITDA</t>
         </is>
       </c>
       <c r="C47" s="11">
-        <f>C20/(C20+C12)</f>
+        <f>C26/C7</f>
         <v/>
       </c>
       <c r="D47" s="11">
-        <f>D20/(D20+D12)</f>
+        <f>D26/D7</f>
         <v/>
       </c>
       <c r="E47" s="11">
-        <f>E20/(E20+E12)</f>
+        <f>E26/E7</f>
         <v/>
       </c>
       <c r="F47" s="11">
-        <f>F20/(F20+F12)</f>
+        <f>F26/F7</f>
         <v/>
       </c>
       <c r="G47" s="11" t="n"/>
-      <c r="H47" s="12">
-        <f>IF(NOT(ISNUMBER(F47)),"",IF(F47&lt;=0.2,"BUY",IF(F47&gt;0.4,"SELL","HOLD")))</f>
-        <v/>
-      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Net debt / (net debt + total assets) (&lt;=20% BUY, &gt;40% SELL)</t>
+          <t>informational; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>15. Deuda financiera neta / market cap</t>
-        </is>
-      </c>
-      <c r="C48" s="11">
-        <f>C20/C30</f>
-        <v/>
-      </c>
-      <c r="D48" s="11">
-        <f>D20/D30</f>
-        <v/>
-      </c>
-      <c r="E48" s="11">
-        <f>E20/E30</f>
-        <v/>
-      </c>
-      <c r="F48" s="11">
-        <f>F20/F30</f>
-        <v/>
-      </c>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="12">
-        <f>IF(NOT(ISNUMBER(F48)),"",IF(F48&lt;=0.15,"BUY",IF(F48&gt;0.4,"SELL","HOLD")))</f>
-        <v/>
-      </c>
+          <t>12. CapEx / D&amp;A</t>
+        </is>
+      </c>
+      <c r="C48" s="13">
+        <f>C26/C10</f>
+        <v/>
+      </c>
+      <c r="D48" s="13">
+        <f>D26/D10</f>
+        <v/>
+      </c>
+      <c r="E48" s="13">
+        <f>E26/E10</f>
+        <v/>
+      </c>
+      <c r="F48" s="13">
+        <f>F26/F10</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="n"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Net debt / market cap (&lt;=15% BUY, &gt;40% SELL)</t>
+          <t>informational; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="8" t="inlineStr">
         <is>
+          <t>13. Ratio de endeudamiento</t>
+        </is>
+      </c>
+      <c r="C49" s="11">
+        <f>C19/C12</f>
+        <v/>
+      </c>
+      <c r="D49" s="11">
+        <f>D19/D12</f>
+        <v/>
+      </c>
+      <c r="E49" s="11">
+        <f>E19/E12</f>
+        <v/>
+      </c>
+      <c r="F49" s="11">
+        <f>F19/F12</f>
+        <v/>
+      </c>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="12">
+        <f>IF(NOT(ISNUMBER(F49)),"",IF(F49&lt;=0.3,"BUY",IF(F49&gt;0.6,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Total debt / total assets (&lt;=30% BUY, &gt;60% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>14. Deuda financiera neta / activos (libros)</t>
+        </is>
+      </c>
+      <c r="C50" s="11">
+        <f>C20/(C20+C12)</f>
+        <v/>
+      </c>
+      <c r="D50" s="11">
+        <f>D20/(D20+D12)</f>
+        <v/>
+      </c>
+      <c r="E50" s="11">
+        <f>E20/(E20+E12)</f>
+        <v/>
+      </c>
+      <c r="F50" s="11">
+        <f>F20/(F20+F12)</f>
+        <v/>
+      </c>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="12">
+        <f>IF(NOT(ISNUMBER(F50)),"",IF(F50&lt;=0.2,"BUY",IF(F50&gt;0.4,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / (net debt + total assets) (&lt;=20% BUY, &gt;40% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>15. Deuda financiera neta / market cap</t>
+        </is>
+      </c>
+      <c r="C51" s="11">
+        <f>C20/C31</f>
+        <v/>
+      </c>
+      <c r="D51" s="11">
+        <f>D20/D31</f>
+        <v/>
+      </c>
+      <c r="E51" s="11">
+        <f>E20/E31</f>
+        <v/>
+      </c>
+      <c r="F51" s="11">
+        <f>F20/F31</f>
+        <v/>
+      </c>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="12">
+        <f>IF(NOT(ISNUMBER(F51)),"",IF(F51&lt;=0.15,"BUY",IF(F51&gt;0.4,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / market cap (&lt;=15% BUY, &gt;40% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
+        <is>
           <t>16. Price estimate (Trefis)</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="H49" s="12">
-        <f>IF(OR(F49="",F29=""),"",IF(F49&gt;F29*1.1,"BUY",IF(F49&lt;F29*0.9,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="H52" s="12">
+        <f>IF(OR(F52="",F30=""),"",IF(F52&gt;F30*1.1,"BUY",IF(F52&lt;F30*0.9,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>External target vs price (&gt;+10% BUY, &lt;-10% SELL)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="16" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Run-rate: 2026-03 (run-rate) annualizes reported year-to-date flows; balance-sheet items are the latest reported quarter (point-in-time).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="17" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Reorganized from Analisis_MSFT_GOOGL_PEP.xlsx (MSFT converted from thousands to millions). Total debt / net debt / dividends / buybacks back-filled from Yahoo Finance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H5:H50">
+  <conditionalFormatting sqref="H5:H53">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BUY"</formula>
     </cfRule>
@@ -2944,7 +3140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I52"/>
+  <dimension ref="B1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="2" max="2"/>
@@ -3317,308 +3513,300 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; intangibles</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>29198</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>31885</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>33380</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>67218</v>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>For tangible book value (P/TBV)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>CASH FLOW</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>Operating cash flow</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="9" t="n">
-        <v>174353</v>
-      </c>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Cash dividend paid</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="9" t="n">
-        <v>7363</v>
-      </c>
-      <c r="E23" s="9" t="n">
-        <v>10049</v>
-      </c>
+          <t>Operating cash flow</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n">
-        <v>10168</v>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Common dividends paid (outflow, shown positive)</t>
-        </is>
+        <v>174353</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Repurchase of capital stock</t>
+          <t>Cash dividend paid</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>61504</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>62222</v>
+        <v>7363</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>45709</v>
+        <v>10049</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>0</v>
+        <v>10168</v>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Buybacks (outflow, shown positive)</t>
+          <t>Common dividends paid (outflow, shown positive)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>CapEx</t>
+          <t>Repurchase of capital stock</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>32251</v>
+        <v>61504</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>52535</v>
+        <v>62222</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>91447</v>
+        <v>45709</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>109924</v>
+        <v>0</v>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Buybacks (outflow, shown positive)</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
+          <t>CapEx</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>32251</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>52535</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>91447</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>109924</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="8" t="inlineStr">
+        <is>
           <t>Free cash flow</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C27" s="9" t="n">
         <v>69495</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D27" s="9" t="n">
         <v>72764</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>73266</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F27" s="9" t="n">
         <v>64429</v>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>MARKET DATA</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Total shares (diluted)</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="n">
-        <v>12630</v>
-      </c>
-      <c r="D28" s="9" t="n">
-        <v>12319</v>
-      </c>
-      <c r="E28" s="9" t="n">
-        <v>12116</v>
-      </c>
-      <c r="F28" s="9" t="n">
-        <v>12095</v>
-      </c>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Market price</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="n">
-        <v>139.69</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>189.3</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>313</v>
-      </c>
-      <c r="F29" s="10" t="n">
-        <v>357.37</v>
+          <t>Total shares (diluted)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>12630</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>12319</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>12116</v>
+      </c>
+      <c r="F29" s="9" t="n">
+        <v>12095</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
         <is>
+          <t>Market price</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="n">
+        <v>139.69</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>189.3</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>313</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>357.37</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="8" t="inlineStr">
+        <is>
           <t>Market cap.</t>
         </is>
       </c>
-      <c r="C30" s="9">
-        <f>C29*C28</f>
-        <v/>
-      </c>
-      <c r="D30" s="9">
-        <f>D29*D28</f>
-        <v/>
-      </c>
-      <c r="E30" s="9">
-        <f>E29*E28</f>
-        <v/>
-      </c>
-      <c r="F30" s="9">
-        <f>F29*F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="C31" s="9">
+        <f>C30*C29</f>
+        <v/>
+      </c>
+      <c r="D31" s="9">
+        <f>D30*D29</f>
+        <v/>
+      </c>
+      <c r="E31" s="9">
+        <f>E30*E29</f>
+        <v/>
+      </c>
+      <c r="F31" s="9">
+        <f>F30*F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>VALUATION &amp; QUALITY RATIOS</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>1. Δ Revenue (YoY)</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11">
-        <f>D6/C6-1</f>
-        <v/>
-      </c>
-      <c r="E32" s="11">
-        <f>E6/D6-1</f>
-        <v/>
-      </c>
-      <c r="F32" s="11">
-        <f>F6/E6-1</f>
-        <v/>
-      </c>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="12">
-        <f>IF(NOT(ISNUMBER(F32)),"",IF(F32&gt;=0.1,"BUY",IF(F32&lt;0,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>YoY revenue growth</t>
-        </is>
-      </c>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>2. Δ Net income (YoY)</t>
+          <t>1. Δ Revenue (YoY)</t>
         </is>
       </c>
       <c r="C33" s="11" t="n"/>
       <c r="D33" s="11">
-        <f>IF(C9&lt;=0,"n.m.",D9/C9-1)</f>
+        <f>D6/C6-1</f>
         <v/>
       </c>
       <c r="E33" s="11">
-        <f>IF(D9&lt;=0,"n.m.",E9/D9-1)</f>
+        <f>E6/D6-1</f>
         <v/>
       </c>
       <c r="F33" s="11">
-        <f>IF(E9&lt;=0,"n.m.",F9/E9-1)</f>
-        <v/>
-      </c>
-      <c r="G33" s="11" t="n"/>
+        <f>F6/E6-1</f>
+        <v/>
+      </c>
       <c r="H33" s="12">
         <f>IF(NOT(ISNUMBER(F33)),"",IF(F33&gt;=0.1,"BUY",IF(F33&lt;0,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>YoY earnings growth (n.m. when prior year &lt;= 0)</t>
+          <t>YoY revenue growth</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="8" t="inlineStr">
         <is>
+          <t>2. Δ Net income (YoY)</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11">
+        <f>IF(C9&lt;=0,1,D9/C9-1)</f>
+        <v/>
+      </c>
+      <c r="E34" s="11">
+        <f>IF(D9&lt;=0,1,E9/D9-1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="11">
+        <f>IF(E9&lt;=0,1,F9/E9-1)</f>
+        <v/>
+      </c>
+      <c r="H34" s="12">
+        <f>IF(NOT(ISNUMBER(F34)),"",IF(F34&gt;=0.1,"BUY",IF(F34&lt;0,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>YoY earnings growth (capped at +100% when prior year &lt;= 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
           <t>3. P/E (trailing)</t>
         </is>
       </c>
-      <c r="C34" s="13">
-        <f>C30/C9</f>
-        <v/>
-      </c>
-      <c r="D34" s="13">
-        <f>D30/D9</f>
-        <v/>
-      </c>
-      <c r="E34" s="13">
-        <f>E30/E9</f>
-        <v/>
-      </c>
-      <c r="F34" s="13">
-        <f>F30/F9</f>
-        <v/>
-      </c>
-      <c r="G34" s="13" t="n"/>
-      <c r="H34" s="12">
-        <f>IF(OR(G34="",NOT(ISNUMBER(F34)),F34&lt;=0),"",IF(F34&lt;G34*0.9,"BUY",IF(F34&gt;G34*1.1,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>Market cap / net income; vs peer median</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Forward P/E</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="n"/>
+      <c r="C35" s="13">
+        <f>C31/C9</f>
+        <v/>
+      </c>
       <c r="D35" s="13">
-        <f>IF(ISNUMBER(D33),D30/(D9*(1+D33)),D30/D9)</f>
+        <f>D31/D9</f>
         <v/>
       </c>
       <c r="E35" s="13">
-        <f>IF(ISNUMBER(E33),E30/(E9*(1+E33)),E30/E9)</f>
+        <f>E31/E9</f>
         <v/>
       </c>
       <c r="F35" s="13">
-        <f>IF(ISNUMBER(F33),F30/(F9*(1+F33)),F30/F9)</f>
+        <f>F31/F9</f>
         <v/>
       </c>
       <c r="G35" s="13" t="n"/>
@@ -3628,158 +3816,159 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>Market cap / net income; vs peer median</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Forward P/E</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="13">
+        <f>IF(ISNUMBER(D34),D31/(D9*(1+D34)),D31/D9)</f>
+        <v/>
+      </c>
+      <c r="E36" s="13">
+        <f>IF(ISNUMBER(E34),E31/(E9*(1+E34)),E31/E9)</f>
+        <v/>
+      </c>
+      <c r="F36" s="13">
+        <f>IF(ISNUMBER(F34),F31/(F9*(1+F34)),F31/F9)</f>
+        <v/>
+      </c>
+      <c r="G36" s="13" t="n"/>
+      <c r="H36" s="12">
+        <f>IF(OR(G36="",NOT(ISNUMBER(F36)),F36&lt;=0),"",IF(F36&lt;G36*0.9,"BUY",IF(F36&gt;G36*1.1,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
           <t>Market cap / (net income * (1 + earnings growth)); vs peer median</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="8" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>4. ROCE</t>
         </is>
       </c>
-      <c r="C36" s="11">
+      <c r="C37" s="11">
         <f>C8/C16</f>
         <v/>
       </c>
-      <c r="D36" s="11">
+      <c r="D37" s="11">
         <f>D8/D16</f>
         <v/>
       </c>
-      <c r="E36" s="11">
+      <c r="E37" s="11">
         <f>E8/E16</f>
         <v/>
       </c>
-      <c r="F36" s="11">
+      <c r="F37" s="11">
         <f>F8/F16</f>
         <v/>
       </c>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="12">
-        <f>IF(NOT(ISNUMBER(F36)),"",IF(F36&gt;=0.15,"BUY",IF(F36&lt;0.08,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="12">
+        <f>IF(NOT(ISNUMBER(F37)),"",IF(F37&gt;=0.15,"BUY",IF(F37&lt;0.08,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
         <is>
           <t>EBIT / capital employed (&gt;=15% BUY, &lt;8% SELL)</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Modified ROCE</t>
-        </is>
-      </c>
-      <c r="C37" s="11">
-        <f>C8/(C30-C17)</f>
-        <v/>
-      </c>
-      <c r="D37" s="11">
-        <f>D8/(D30-D17)</f>
-        <v/>
-      </c>
-      <c r="E37" s="11">
-        <f>E8/(E30-E17)</f>
-        <v/>
-      </c>
-      <c r="F37" s="11">
-        <f>F8/(F30-F17)</f>
-        <v/>
-      </c>
-      <c r="G37" s="11" t="n"/>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>EBIT / (market cap - equity)</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>5. EV / EBITDA</t>
-        </is>
-      </c>
-      <c r="C38" s="13">
-        <f>(C30+C18-C13)/C7</f>
-        <v/>
-      </c>
-      <c r="D38" s="13">
-        <f>(D30+D18-D13)/D7</f>
-        <v/>
-      </c>
-      <c r="E38" s="13">
-        <f>(E30+E18-E13)/E7</f>
-        <v/>
-      </c>
-      <c r="F38" s="13">
-        <f>(F30+F18-F13)/F7</f>
-        <v/>
-      </c>
-      <c r="G38" s="13" t="n"/>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ROE</t>
+        </is>
+      </c>
+      <c r="C38" s="11">
+        <f>C9/C17</f>
+        <v/>
+      </c>
+      <c r="D38" s="11">
+        <f>D9/D17</f>
+        <v/>
+      </c>
+      <c r="E38" s="11">
+        <f>E9/E17</f>
+        <v/>
+      </c>
+      <c r="F38" s="11">
+        <f>F9/F17</f>
+        <v/>
+      </c>
+      <c r="G38" s="11" t="n"/>
       <c r="H38" s="12">
-        <f>IF(OR(G38="",NOT(ISNUMBER(F38)),F38&lt;=0),"",IF(F38&lt;G38*0.9,"BUY",IF(F38&gt;G38*1.1,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F38)),"",IF(F38&gt;=0.15,"BUY",IF(F38&lt;0.08,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Enterprise value / EBITDA; vs peer median</t>
+          <t>Net income / equity — works for banks (&gt;=15% BUY, &lt;8% SELL)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>6. P / B</t>
-        </is>
-      </c>
-      <c r="C39" s="13">
-        <f>C30/C17</f>
-        <v/>
-      </c>
-      <c r="D39" s="13">
-        <f>D30/D17</f>
-        <v/>
-      </c>
-      <c r="E39" s="13">
-        <f>E30/E17</f>
-        <v/>
-      </c>
-      <c r="F39" s="13">
-        <f>F30/F17</f>
-        <v/>
-      </c>
-      <c r="G39" s="13" t="n"/>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Acid ROCE</t>
+        </is>
+      </c>
+      <c r="C39" s="11">
+        <f>C8/(C31-C17)</f>
+        <v/>
+      </c>
+      <c r="D39" s="11">
+        <f>D8/(D31-D17)</f>
+        <v/>
+      </c>
+      <c r="E39" s="11">
+        <f>E8/(E31-E17)</f>
+        <v/>
+      </c>
+      <c r="F39" s="11">
+        <f>F8/(F31-F17)</f>
+        <v/>
+      </c>
+      <c r="G39" s="11" t="n"/>
       <c r="H39" s="12">
-        <f>IF(OR(G39="",NOT(ISNUMBER(F39)),F39&lt;=0),"",IF(F39&lt;G39*0.9,"BUY",IF(F39&gt;G39*1.1,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F39)),"",IF(F39&gt;=0.05,"BUY",IF(F39&lt;0.04,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>vs peer median</t>
+          <t>EBIT / (market cap - equity) (&gt;=5% BUY, 4-5% HOLD, &lt;4% SELL)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>7. P / S</t>
+          <t>5. EV / EBITDA</t>
         </is>
       </c>
       <c r="C40" s="13">
-        <f>C30/C6</f>
+        <f>(C31+C18-C13)/C7</f>
         <v/>
       </c>
       <c r="D40" s="13">
-        <f>D30/D6</f>
+        <f>(D31+D18-D13)/D7</f>
         <v/>
       </c>
       <c r="E40" s="13">
-        <f>E30/E6</f>
+        <f>(E31+E18-E13)/E7</f>
         <v/>
       </c>
       <c r="F40" s="13">
-        <f>F30/F6</f>
+        <f>(F31+F18-F13)/F7</f>
         <v/>
       </c>
       <c r="G40" s="13" t="n"/>
@@ -3789,30 +3978,30 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>vs peer median</t>
+          <t>Enterprise value / EBITDA; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>8. EV / FCF</t>
+          <t>6. P / B</t>
         </is>
       </c>
       <c r="C41" s="13">
-        <f>(C30+C18-C13)/C26</f>
+        <f>C31/C17</f>
         <v/>
       </c>
       <c r="D41" s="13">
-        <f>(D30+D18-D13)/D26</f>
+        <f>D31/D17</f>
         <v/>
       </c>
       <c r="E41" s="13">
-        <f>(E30+E18-E13)/E26</f>
+        <f>E31/E17</f>
         <v/>
       </c>
       <c r="F41" s="13">
-        <f>(F30+F18-F13)/F26</f>
+        <f>F31/F17</f>
         <v/>
       </c>
       <c r="G41" s="13" t="n"/>
@@ -3827,255 +4016,362 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>9. Dividend yield</t>
-        </is>
-      </c>
-      <c r="C42" s="15" t="n"/>
-      <c r="D42" s="15" t="n">
-        <v>0.00316957210776545</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>0.0026517571884984</v>
-      </c>
-      <c r="F42" s="15" t="n"/>
+      <c r="B42" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P / TBV</t>
+        </is>
+      </c>
+      <c r="C42" s="13">
+        <f>C31/(C17-C21)</f>
+        <v/>
+      </c>
+      <c r="D42" s="13">
+        <f>D31/(D17-D21)</f>
+        <v/>
+      </c>
+      <c r="E42" s="13">
+        <f>E31/(E17-E21)</f>
+        <v/>
+      </c>
+      <c r="F42" s="13">
+        <f>F31/(F17-F21)</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="12">
-        <f>IF(NOT(ISNUMBER(F42)),"",IF(F42&gt;=0.03,"BUY",IF(F42&lt;0.01,"SELL","HOLD")))</f>
+        <f>IF(OR(G42="",NOT(ISNUMBER(F42)),F42&lt;=0),"",IF(F42&lt;G42*0.9,"BUY",IF(F42&gt;G42*1.1,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>&gt;=3% BUY, &lt;1% SELL</t>
+          <t>Price / tangible book — key for banks; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>10. Total shareholder return</t>
-        </is>
-      </c>
-      <c r="C43" s="11">
-        <f>(C23+C24)/C30</f>
-        <v/>
-      </c>
-      <c r="D43" s="11">
-        <f>(D23+D24)/D30</f>
-        <v/>
-      </c>
-      <c r="E43" s="11">
-        <f>(E23+E24)/E30</f>
-        <v/>
-      </c>
-      <c r="F43" s="11">
-        <f>(F23+F24)/F30</f>
-        <v/>
-      </c>
-      <c r="G43" s="11" t="n"/>
+          <t>7. P / S</t>
+        </is>
+      </c>
+      <c r="C43" s="13">
+        <f>C31/C6</f>
+        <v/>
+      </c>
+      <c r="D43" s="13">
+        <f>D31/D6</f>
+        <v/>
+      </c>
+      <c r="E43" s="13">
+        <f>E31/E6</f>
+        <v/>
+      </c>
+      <c r="F43" s="13">
+        <f>F31/F6</f>
+        <v/>
+      </c>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="12">
-        <f>IF(NOT(ISNUMBER(F43)),"",IF(F43&gt;=0.05,"BUY",IF(F43&lt;0.02,"SELL","HOLD")))</f>
+        <f>IF(OR(G43="",NOT(ISNUMBER(F43)),F43&lt;=0),"",IF(F43&lt;G43*0.9,"BUY",IF(F43&gt;G43*1.1,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>(dividends + buybacks) / market cap (&gt;=5% BUY, &lt;2% SELL)</t>
+          <t>vs peer median</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>11. CapEx / EBITDA</t>
-        </is>
-      </c>
-      <c r="C44" s="11">
-        <f>C25/C7</f>
-        <v/>
-      </c>
-      <c r="D44" s="11">
-        <f>D25/D7</f>
-        <v/>
-      </c>
-      <c r="E44" s="11">
-        <f>E25/E7</f>
-        <v/>
-      </c>
-      <c r="F44" s="11">
-        <f>F25/F7</f>
-        <v/>
-      </c>
-      <c r="G44" s="11" t="n"/>
+          <t>8. EV / FCF</t>
+        </is>
+      </c>
+      <c r="C44" s="13">
+        <f>(C31+C18-C13)/C27</f>
+        <v/>
+      </c>
+      <c r="D44" s="13">
+        <f>(D31+D18-D13)/D27</f>
+        <v/>
+      </c>
+      <c r="E44" s="13">
+        <f>(E31+E18-E13)/E27</f>
+        <v/>
+      </c>
+      <c r="F44" s="13">
+        <f>(F31+F18-F13)/F27</f>
+        <v/>
+      </c>
+      <c r="G44" s="13" t="n"/>
+      <c r="H44" s="12">
+        <f>IF(OR(G44="",NOT(ISNUMBER(F44)),F44&lt;=0),"",IF(F44&lt;G44*0.9,"BUY",IF(F44&gt;G44*1.1,"SELL","HOLD")))</f>
+        <v/>
+      </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>informational; vs peer median</t>
+          <t>vs peer median</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>12. CapEx / D&amp;A</t>
-        </is>
-      </c>
-      <c r="C45" s="13">
-        <f>C25/C10</f>
-        <v/>
-      </c>
-      <c r="D45" s="13">
-        <f>D25/D10</f>
-        <v/>
-      </c>
-      <c r="E45" s="13">
-        <f>E25/E10</f>
-        <v/>
-      </c>
-      <c r="F45" s="13">
-        <f>F25/F10</f>
-        <v/>
-      </c>
-      <c r="G45" s="13" t="n"/>
+          <t>9. Dividend yield</t>
+        </is>
+      </c>
+      <c r="C45" s="15">
+        <f>C24/C31</f>
+        <v/>
+      </c>
+      <c r="D45" s="15">
+        <f>D24/D31</f>
+        <v/>
+      </c>
+      <c r="E45" s="15">
+        <f>E24/E31</f>
+        <v/>
+      </c>
+      <c r="F45" s="15">
+        <f>F24/F31</f>
+        <v/>
+      </c>
+      <c r="H45" s="12">
+        <f>IF(NOT(ISNUMBER(F45)),"",IF(F45&gt;=0.03,"BUY",IF(F45&lt;0.01,"SELL","HOLD")))</f>
+        <v/>
+      </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>informational; vs peer median</t>
+          <t>Dividends paid / market cap (&gt;=3% BUY, &lt;1% SELL)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>13. Ratio de endeudamiento</t>
+          <t>10. Total shareholder return</t>
         </is>
       </c>
       <c r="C46" s="11">
-        <f>C19/C12</f>
+        <f>(C24+C25)/C31</f>
         <v/>
       </c>
       <c r="D46" s="11">
-        <f>D19/D12</f>
+        <f>(D24+D25)/D31</f>
         <v/>
       </c>
       <c r="E46" s="11">
-        <f>E19/E12</f>
+        <f>(E24+E25)/E31</f>
         <v/>
       </c>
       <c r="F46" s="11">
-        <f>F19/F12</f>
+        <f>(F24+F25)/F31</f>
         <v/>
       </c>
       <c r="G46" s="11" t="n"/>
       <c r="H46" s="12">
-        <f>IF(NOT(ISNUMBER(F46)),"",IF(F46&lt;=0.3,"BUY",IF(F46&gt;0.6,"SELL","HOLD")))</f>
+        <f>IF(NOT(ISNUMBER(F46)),"",IF(F46&gt;=0.05,"BUY",IF(F46&lt;0.02,"SELL","HOLD")))</f>
         <v/>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Total debt / total assets (&lt;=30% BUY, &gt;60% SELL)</t>
+          <t>(dividends + buybacks) / market cap (&gt;=5% BUY, &lt;2% SELL)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>14. Deuda financiera neta / activos (libros)</t>
+          <t>11. CapEx / EBITDA</t>
         </is>
       </c>
       <c r="C47" s="11">
-        <f>C20/(C20+C12)</f>
+        <f>C26/C7</f>
         <v/>
       </c>
       <c r="D47" s="11">
-        <f>D20/(D20+D12)</f>
+        <f>D26/D7</f>
         <v/>
       </c>
       <c r="E47" s="11">
-        <f>E20/(E20+E12)</f>
+        <f>E26/E7</f>
         <v/>
       </c>
       <c r="F47" s="11">
-        <f>F20/(F20+F12)</f>
+        <f>F26/F7</f>
         <v/>
       </c>
       <c r="G47" s="11" t="n"/>
-      <c r="H47" s="12">
-        <f>IF(NOT(ISNUMBER(F47)),"",IF(F47&lt;=0.2,"BUY",IF(F47&gt;0.4,"SELL","HOLD")))</f>
-        <v/>
-      </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Net debt / (net debt + total assets) (&lt;=20% BUY, &gt;40% SELL)</t>
+          <t>informational; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>15. Deuda financiera neta / market cap</t>
-        </is>
-      </c>
-      <c r="C48" s="11">
-        <f>C20/C30</f>
-        <v/>
-      </c>
-      <c r="D48" s="11">
-        <f>D20/D30</f>
-        <v/>
-      </c>
-      <c r="E48" s="11">
-        <f>E20/E30</f>
-        <v/>
-      </c>
-      <c r="F48" s="11">
-        <f>F20/F30</f>
-        <v/>
-      </c>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="12">
-        <f>IF(NOT(ISNUMBER(F48)),"",IF(F48&lt;=0.15,"BUY",IF(F48&gt;0.4,"SELL","HOLD")))</f>
-        <v/>
-      </c>
+          <t>12. CapEx / D&amp;A</t>
+        </is>
+      </c>
+      <c r="C48" s="13">
+        <f>C26/C10</f>
+        <v/>
+      </c>
+      <c r="D48" s="13">
+        <f>D26/D10</f>
+        <v/>
+      </c>
+      <c r="E48" s="13">
+        <f>E26/E10</f>
+        <v/>
+      </c>
+      <c r="F48" s="13">
+        <f>F26/F10</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="n"/>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Net debt / market cap (&lt;=15% BUY, &gt;40% SELL)</t>
+          <t>informational; vs peer median</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="8" t="inlineStr">
         <is>
+          <t>13. Ratio de endeudamiento</t>
+        </is>
+      </c>
+      <c r="C49" s="11">
+        <f>C19/C12</f>
+        <v/>
+      </c>
+      <c r="D49" s="11">
+        <f>D19/D12</f>
+        <v/>
+      </c>
+      <c r="E49" s="11">
+        <f>E19/E12</f>
+        <v/>
+      </c>
+      <c r="F49" s="11">
+        <f>F19/F12</f>
+        <v/>
+      </c>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="12">
+        <f>IF(NOT(ISNUMBER(F49)),"",IF(F49&lt;=0.3,"BUY",IF(F49&gt;0.6,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Total debt / total assets (&lt;=30% BUY, &gt;60% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>14. Deuda financiera neta / activos (libros)</t>
+        </is>
+      </c>
+      <c r="C50" s="11">
+        <f>C20/(C20+C12)</f>
+        <v/>
+      </c>
+      <c r="D50" s="11">
+        <f>D20/(D20+D12)</f>
+        <v/>
+      </c>
+      <c r="E50" s="11">
+        <f>E20/(E20+E12)</f>
+        <v/>
+      </c>
+      <c r="F50" s="11">
+        <f>F20/(F20+F12)</f>
+        <v/>
+      </c>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="12">
+        <f>IF(NOT(ISNUMBER(F50)),"",IF(F50&lt;=0.2,"BUY",IF(F50&gt;0.4,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / (net debt + total assets) (&lt;=20% BUY, &gt;40% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>15. Deuda financiera neta / market cap</t>
+        </is>
+      </c>
+      <c r="C51" s="11">
+        <f>C20/C31</f>
+        <v/>
+      </c>
+      <c r="D51" s="11">
+        <f>D20/D31</f>
+        <v/>
+      </c>
+      <c r="E51" s="11">
+        <f>E20/E31</f>
+        <v/>
+      </c>
+      <c r="F51" s="11">
+        <f>F20/F31</f>
+        <v/>
+      </c>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="12">
+        <f>IF(NOT(ISNUMBER(F51)),"",IF(F51&lt;=0.15,"BUY",IF(F51&gt;0.4,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Net debt / market cap (&lt;=15% BUY, &gt;40% SELL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="8" t="inlineStr">
+        <is>
           <t>16. Price estimate (Trefis)</t>
         </is>
       </c>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-      <c r="E49" s="10" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="H49" s="12">
-        <f>IF(OR(F49="",F29=""),"",IF(F49&gt;F29*1.1,"BUY",IF(F49&lt;F29*0.9,"SELL","HOLD")))</f>
-        <v/>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="10" t="n"/>
+      <c r="F52" s="10" t="n"/>
+      <c r="H52" s="12">
+        <f>IF(OR(F52="",F30=""),"",IF(F52&gt;F30*1.1,"BUY",IF(F52&lt;F30*0.9,"SELL","HOLD")))</f>
+        <v/>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>External target vs price (&gt;+10% BUY, &lt;-10% SELL)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="B51" s="16" t="inlineStr">
+    <row r="54">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>Run-rate: 2026-03 (run-rate) annualizes reported year-to-date flows; balance-sheet items are the latest reported quarter (point-in-time).</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="B52" s="17" t="inlineStr">
+    <row r="55">
+      <c r="B55" s="17" t="inlineStr">
         <is>
           <t>Reorganized from Analisis_MSFT_GOOGL_PEP.xlsx (MSFT converted from thousands to millions). Total debt / net debt / dividends / buybacks back-filled from Yahoo Finance.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="H5:H50">
+  <conditionalFormatting sqref="H5:H53">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"BUY"</formula>
     </cfRule>
